--- a/exercices/correction_examen_blanc2026.xlsx
+++ b/exercices/correction_examen_blanc2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B63161E1-59FE-4E0A-B1B8-DEF1F03C80F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6D26B2-AE96-403F-AA18-6D2374A12096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" xr2:uid="{FCA47228-19CC-4D78-8081-8A410B43A799}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{FCA47228-19CC-4D78-8081-8A410B43A799}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Examen blanc contrôle continu</t>
   </si>
@@ -55,6 +66,12 @@
   </si>
   <si>
     <t xml:space="preserve">Les données sont bien importées depuis dbnomics, mais le dataframe n'est pas construit. PPA: graphique correcte mais réponse partiellement fausse. Le PIB nominal par habitant et PIB réel par habitant en PPA mal calculés. Code pour le dernier exercice erroné. </t>
+  </si>
+  <si>
+    <t>Le tableau contient bien toutes les variables mais contient trois variables pour les années en trop. Graphique pour la PPA correct mais l'interprétation est vague. Le PIB constant en PPA est est faux. Tableau des taux de croissance pas fait.</t>
+  </si>
+  <si>
+    <t>Les variables sont bien importées mais le tableau n'est pas construit. Le deuxième exercice manque.</t>
   </si>
 </sst>
 </file>
@@ -92,10 +109,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -114,9 +131,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -154,7 +171,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -260,7 +277,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -402,7 +419,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -410,24 +427,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DBD0ED7-BEA5-4E6C-A87C-0133F7CC2163}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -444,11 +461,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>23306145</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>1.5</v>
       </c>
       <c r="C4">
@@ -461,7 +478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>23829039</v>
       </c>
@@ -478,7 +495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>23510357</v>
       </c>
@@ -497,7 +514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>23404031</v>
       </c>
@@ -514,6 +531,42 @@
       </c>
       <c r="E7" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>24315152</v>
+      </c>
+      <c r="B8">
+        <v>2.75</v>
+      </c>
+      <c r="C8">
+        <f>0.75+0.25+0</f>
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <f>C8+B8</f>
+        <v>3.75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>24300568</v>
+      </c>
+      <c r="B9">
+        <v>2.5</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>2.5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/exercices/correction_examen_blanc2026.xlsx
+++ b/exercices/correction_examen_blanc2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6D26B2-AE96-403F-AA18-6D2374A12096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EF4BDE-3114-4510-823A-C89BC8A3446F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{FCA47228-19CC-4D78-8081-8A410B43A799}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>Commentaire</t>
   </si>
   <si>
-    <t>Aucun exercice complété</t>
-  </si>
-  <si>
     <t>Il ne manque que le calcul des taux de croissances moyens pour le dernier exercice</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>Les variables sont bien importées mais le tableau n'est pas construit. Le deuxième exercice manque.</t>
+  </si>
+  <si>
+    <t>Les variables sont importées depuis le csv plutôt que depuis dbnomics. Le deuxième exercice n'est pas complété.</t>
   </si>
 </sst>
 </file>
@@ -475,7 +475,7 @@
         <v>2.5</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -511,7 +511,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -530,7 +530,7 @@
         <v>3.75</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -549,7 +549,7 @@
         <v>3.75</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -566,7 +566,7 @@
         <v>2.5</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/exercices/correction_examen_blanc2026.xlsx
+++ b/exercices/correction_examen_blanc2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EF4BDE-3114-4510-823A-C89BC8A3446F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8848185-A8CF-4097-981E-73B56A8F62B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{FCA47228-19CC-4D78-8081-8A410B43A799}"/>
+    <workbookView xWindow="29940" yWindow="1140" windowWidth="18900" windowHeight="10830" xr2:uid="{FCA47228-19CC-4D78-8081-8A410B43A799}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>Examen blanc contrôle continu</t>
   </si>
@@ -72,6 +72,27 @@
   </si>
   <si>
     <t>Les variables sont importées depuis le csv plutôt que depuis dbnomics. Le deuxième exercice n'est pas complété.</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>Note finale après le deuxième rendu</t>
+  </si>
+  <si>
+    <t>Bonus de second rendu</t>
+  </si>
+  <si>
+    <t>Note final</t>
+  </si>
+  <si>
+    <t>Bonus maximal de 2 points</t>
+  </si>
+  <si>
+    <t>Petite erreur dans le calcul du tableau final</t>
+  </si>
+  <si>
+    <t>Quelques erreurs dans le calcul du PIB réel</t>
   </si>
 </sst>
 </file>
@@ -87,15 +108,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,16 +130,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,8 +470,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DBD0ED7-BEA5-4E6C-A87C-0133F7CC2163}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="22.453125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
@@ -488,8 +534,8 @@
       <c r="C5">
         <v>2.5</v>
       </c>
-      <c r="D5">
-        <v>5</v>
+      <c r="D5" t="s">
+        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -569,9 +615,171 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>23306145</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>2.5</v>
+      </c>
+      <c r="E13">
+        <v>1.75</v>
+      </c>
+      <c r="F13" s="3">
+        <f>E13+D13</f>
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>23829039</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>2.5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>23510357</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <f>0.25+1+0.75</f>
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <f>C15+B15</f>
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>6</v>
+      </c>
+      <c r="G15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>23404031</v>
+      </c>
+      <c r="B16">
+        <v>2.5</v>
+      </c>
+      <c r="C16">
+        <f>0.75+0.5</f>
+        <v>1.25</v>
+      </c>
+      <c r="D16">
+        <f>C16+B16</f>
+        <v>3.75</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>24315152</v>
+      </c>
+      <c r="B17">
+        <v>2.75</v>
+      </c>
+      <c r="C17">
+        <f>0.75+0.25+0</f>
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <f>C17+B17</f>
+        <v>3.75</v>
+      </c>
+      <c r="E17">
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="3">
+        <f>E17+D17</f>
+        <v>5.25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>24300568</v>
+      </c>
+      <c r="B18">
+        <v>2.5</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>2.5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/exercices/correction_examen_blanc2026.xlsx
+++ b/exercices/correction_examen_blanc2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8848185-A8CF-4097-981E-73B56A8F62B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7992914-24B8-4F8A-87AB-F2E090B06288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29940" yWindow="1140" windowWidth="18900" windowHeight="10830" xr2:uid="{FCA47228-19CC-4D78-8081-8A410B43A799}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{FCA47228-19CC-4D78-8081-8A410B43A799}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Examen blanc contrôle continu</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Quelques erreurs dans le calcul du PIB réel</t>
+  </si>
+  <si>
+    <t>Pas de second rendu</t>
   </si>
 </sst>
 </file>
@@ -152,10 +155,10 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,18 +480,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -616,12 +619,12 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -639,7 +642,7 @@
       <c r="E12" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -659,7 +662,7 @@
       <c r="E13">
         <v>1.75</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f>E13+D13</f>
         <v>4.25</v>
       </c>
@@ -677,7 +680,10 @@
       <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="3">
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="2">
         <v>5.5</v>
       </c>
     </row>
@@ -699,7 +705,7 @@
       <c r="E15">
         <v>1.5</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" t="s">
@@ -724,7 +730,7 @@
       <c r="E16">
         <v>2</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>5.75</v>
       </c>
     </row>
@@ -746,7 +752,7 @@
       <c r="E17">
         <v>1.5</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <f>E17+D17</f>
         <v>5.25</v>
       </c>
@@ -767,7 +773,10 @@
       <c r="D18">
         <v>2.5</v>
       </c>
-      <c r="F18" s="3">
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="2">
         <v>2.5</v>
       </c>
     </row>
